--- a/artfynd/A 54621-2023 artfynd.xlsx
+++ b/artfynd/A 54621-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54621-2023 artfynd.xlsx
+++ b/artfynd/A 54621-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56052004</v>
+        <v>56052003</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598963.624642969</v>
+        <v>598860</v>
       </c>
       <c r="R2" t="n">
-        <v>6980228.785432748</v>
+        <v>6980085</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2015-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +771,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # högstubbe tall</t>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56052005</v>
+        <v>56052004</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598974.3297638666</v>
+        <v>598964</v>
       </c>
       <c r="R3" t="n">
-        <v>6980236.855307674</v>
+        <v>6980229</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,19 +861,9 @@
           <t>2015-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +885,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # brandstubbe</t>
+          <t>1 substratenheter # högstubbe tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56052003</v>
+        <v>56052005</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598860.29631238</v>
+        <v>598974</v>
       </c>
       <c r="R4" t="n">
-        <v>6980085.324762267</v>
+        <v>6980237</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,19 +975,9 @@
           <t>2015-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +999,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>1 substratenheter # brandstubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1059,6 +1014,119 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107721782</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vackerhöjden, Stor-Gussjön, Liden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598890</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6980125</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54621-2023 artfynd.xlsx
+++ b/artfynd/A 54621-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56052003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56052004</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56052005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,8 +1147,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107721782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>